--- a/weekly_report.xlsx
+++ b/weekly_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\05_report_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A2DEA-FBE7-4BE5-9F27-B7651ACB4420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538116DB-1423-4234-8520-07A17707FB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7752" yWindow="1656" windowWidth="14028" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="report" sheetId="1" r:id="rId1"/>
@@ -351,6 +351,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -358,24 +376,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -668,13 +668,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="15"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -682,19 +682,19 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="2"/>
@@ -704,7 +704,7 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -721,7 +721,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -736,21 +736,21 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -767,7 +767,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
@@ -782,21 +782,21 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -813,7 +813,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
@@ -828,14 +828,14 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -850,5 +850,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/weekly_report.xlsx
+++ b/weekly_report.xlsx
@@ -1,174 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\develop\05_report_tool\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538116DB-1423-4234-8520-07A17707FB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7752" yWindow="1656" windowWidth="14028" windowHeight="11208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="report" sheetId="1" r:id="rId1"/>
+    <sheet name="report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
-  <si>
-    <t>周报</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进展</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>处理人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质量改进</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效率提升</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题进展</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题AAAAAAAA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题BBBBBBBBB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质量AAAAAAAA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质量BBBBBBBBB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效率提升AAAAAAAA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效率提升BBBBBBBBB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘明睿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蒋雨涵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>close</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>open</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题录入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质量提升20%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>代码自动review功能已开展</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维护效率提升50%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开发效率提升20%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线 Light"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="等线 Light"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -181,18 +70,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -335,63 +224,250 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -657,199 +733,423 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="34.33203125" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col width="34.33203125" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15.44140625" customWidth="1" min="4" max="5"/>
+    <col width="14.88671875" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6"/>
+    <row r="1" ht="33" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>周报</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="33" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>进展</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>问题进展</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>问题AAAAAAAA</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>问题录入</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>刘明睿</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>问题BBBBBBBBB</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>问题录入</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>蒋雨涵</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>质量改进</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>质量AAAAAAAA</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>质量提升20%</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>刘明睿</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>质量BBBBBBBBB</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>代码自动review功能已开展</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>蒋雨涵</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>效率提升</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>效率提升AAAAAAAA</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>维护效率提升50%</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>蒋雨涵</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>效率提升BBBBBBBBB</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>开发效率提升20%</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>刘明睿</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="14.4" customHeight="1" thickBot="1">
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>吴迪</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>刘明睿</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="14.4" customHeight="1" thickBot="1">
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>